--- a/data/analysis_panns/sound_event_eval_panns_w1_0s_h0_5s.xlsx
+++ b/data/analysis_panns/sound_event_eval_panns_w1_0s_h0_5s.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="29">
   <si>
     <t>event</t>
   </si>
@@ -81,49 +81,40 @@
     <t>NO</t>
   </si>
   <si>
-    <t>speech(0-60), animal(48-144), music(60-96), speech(108-156), music(144-180), silence(168-192), engine(180-240)</t>
-  </si>
-  <si>
-    <t>speech(0-180), music(168-216), engine(180-240)</t>
-  </si>
-  <si>
-    <t>speech(0-120), engine(108-240)</t>
+    <t>engine(180-240)</t>
+  </si>
+  <si>
+    <t>engine(108-240)</t>
   </si>
   <si>
     <t>YES</t>
   </si>
   <si>
-    <t>speech(0-108), burst_pop(96-120), door(108-132), gunshot_or_explosion(120-156), engine(144-240)</t>
-  </si>
-  <si>
-    <t>engine(0-60), door(48-72), gunshot_or_explosion(60-96), engine(84-192), speech(96-132), music(144-228), speech(180-204), engine(216-240)</t>
-  </si>
-  <si>
-    <t>silence(0-36), engine(24-72), music(60-84), speech(72-132), gunshot_or_explosion(120-144), music(132-192), engine(144-240)</t>
-  </si>
-  <si>
-    <t>music(0-24), gunshot_or_explosion(12-36), engine(24-240), speech(108-132), speech(156-180)</t>
-  </si>
-  <si>
-    <t>engine(0-24), silence(12-36), music(24-48), gunshot_or_explosion(36-72), engine(60-240), speech(108-144), music(156-180)</t>
-  </si>
-  <si>
-    <t>engine(0-240), silence(24-48), door(36-60), music(60-96)</t>
-  </si>
-  <si>
-    <t>music(0-60), engine(12-240), silence(60-84)</t>
-  </si>
-  <si>
-    <t>engine(0-240), silence(12-36), music(204-228)</t>
-  </si>
-  <si>
-    <t>engine(0-240), horn(12-48), music(72-96), music(132-156), music(192-216)</t>
-  </si>
-  <si>
-    <t>engine(0-156), music(60-84), speech(144-228), engine(216-240)</t>
-  </si>
-  <si>
-    <t>engine(0-240), music(72-96), silence(168-228)</t>
+    <t>gunshot_or_explosion(96-156), engine(144-240)</t>
+  </si>
+  <si>
+    <t>engine(0-60), gunshot_or_explosion(60-96), engine(84-192), engine(216-240)</t>
+  </si>
+  <si>
+    <t>engine(24-72), gunshot_or_explosion(120-144), engine(144-240)</t>
+  </si>
+  <si>
+    <t>gunshot_or_explosion(12-36), engine(24-240)</t>
+  </si>
+  <si>
+    <t>engine(0-24), gunshot_or_explosion(36-72), engine(60-240)</t>
+  </si>
+  <si>
+    <t>engine(0-240)</t>
+  </si>
+  <si>
+    <t>engine(12-240)</t>
+  </si>
+  <si>
+    <t>engine(0-240), horn(12-48)</t>
+  </si>
+  <si>
+    <t>engine(0-156), engine(216-240)</t>
   </si>
 </sst>
 </file>
@@ -655,6 +646,50 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>26</v>
       </c>
     </row>
@@ -663,31 +698,31 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>13</v>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>14</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -699,6 +734,50 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>27</v>
       </c>
     </row>
@@ -707,481 +786,437 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>17</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
       <c r="E2" t="s">
         <v>24</v>
       </c>
@@ -1189,48 +1224,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/data/analysis_panns/sound_event_eval_panns_w1_0s_h0_5s.xlsx
+++ b/data/analysis_panns/sound_event_eval_panns_w1_0s_h0_5s.xlsx
@@ -22,13 +22,19 @@
     <sheet name="Scene_15" sheetId="13" r:id="rId13"/>
     <sheet name="Scene_16" sheetId="14" r:id="rId14"/>
     <sheet name="Scene_17" sheetId="15" r:id="rId15"/>
+    <sheet name="Scene_29" sheetId="16" r:id="rId16"/>
+    <sheet name="Scene_30" sheetId="17" r:id="rId17"/>
+    <sheet name="Scene_31" sheetId="18" r:id="rId18"/>
+    <sheet name="Scene_32" sheetId="19" r:id="rId19"/>
+    <sheet name="Scene_33" sheetId="20" r:id="rId20"/>
+    <sheet name="Scene_34" sheetId="21" r:id="rId21"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="34">
   <si>
     <t>event</t>
   </si>
@@ -115,6 +121,21 @@
   </si>
   <si>
     <t>engine(0-156), engine(216-240)</t>
+  </si>
+  <si>
+    <t>engine(36-60), engine(96-240)</t>
+  </si>
+  <si>
+    <t>engine(0-36), engine(60-240)</t>
+  </si>
+  <si>
+    <t>engine(0-216), horn(24-72)</t>
+  </si>
+  <si>
+    <t>engine(0-168), gunshot_or_explosion(48-72), engine(204-228)</t>
+  </si>
+  <si>
+    <t>engine(0-168), engine(204-228), gunshot_or_explosion(48-72)</t>
   </si>
 </sst>
 </file>
@@ -874,6 +895,176 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
@@ -918,6 +1109,111 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>

--- a/data/analysis_panns/sound_event_eval_panns_w1_0s_h0_5s.xlsx
+++ b/data/analysis_panns/sound_event_eval_panns_w1_0s_h0_5s.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="33">
   <si>
     <t>event</t>
   </si>
@@ -99,7 +99,7 @@
     <t>gunshot_or_explosion(96-156), engine(144-240)</t>
   </si>
   <si>
-    <t>engine(0-60), gunshot_or_explosion(60-96), engine(84-192), engine(216-240)</t>
+    <t>engine(0-240), gunshot_or_explosion(60-96)</t>
   </si>
   <si>
     <t>engine(24-72), gunshot_or_explosion(120-144), engine(144-240)</t>
@@ -124,9 +124,6 @@
   </si>
   <si>
     <t>engine(36-60), engine(96-240)</t>
-  </si>
-  <si>
-    <t>engine(0-36), engine(60-240)</t>
   </si>
   <si>
     <t>engine(0-216), horn(24-72)</t>
@@ -1057,6 +1054,94 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1065,34 +1150,34 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
@@ -1101,95 +1186,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
         <v>31</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>34</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1206,7 +1203,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
